--- a/Assets/Data/Dungeon0052.xlsx
+++ b/Assets/Data/Dungeon0052.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7960" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="28">
   <si>
     <t>Id</t>
   </si>
@@ -52,16 +52,31 @@
     <t>■</t>
   </si>
   <si>
-    <t>Ev</t>
+    <t>Mv</t>
   </si>
   <si>
     <t>Ba</t>
   </si>
   <si>
-    <t>Mv</t>
+    <t>No</t>
   </si>
   <si>
-    <t>Dm</t>
+    <t>Ev</t>
+  </si>
+  <si>
+    <t>Tr:D2</t>
+  </si>
+  <si>
+    <t>①</t>
+  </si>
+  <si>
+    <t>②</t>
+  </si>
+  <si>
+    <t>④</t>
+  </si>
+  <si>
+    <t>③</t>
   </si>
   <si>
     <t>PositionX</t>
@@ -96,10 +111,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -117,47 +132,37 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -172,7 +177,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -180,14 +185,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -202,21 +200,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -231,7 +231,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -243,6 +243,14 @@
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -260,6 +268,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -270,7 +285,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -282,67 +327,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -360,7 +363,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -372,19 +387,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -396,43 +435,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -448,12 +469,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -464,20 +479,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -497,17 +509,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -526,8 +532,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -561,6 +567,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -569,145 +584,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -730,12 +745,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -823,169 +838,193 @@
         </row>
         <row r="4">
           <cell r="D4">
-            <v>2010</v>
+            <v>1020</v>
           </cell>
           <cell r="E4" t="str">
-            <v>ダンジョンから出る</v>
+            <v>エンフェリアイベント再生</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2020</v>
+            <v>1030</v>
           </cell>
           <cell r="E5" t="str">
-            <v>ダンジョン移動</v>
+            <v>メインイベント再生</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6">
-            <v>2021</v>
+            <v>2010</v>
           </cell>
           <cell r="E6" t="str">
-            <v>移動判定なしでダンジョン移動</v>
+            <v>ダンジョンから出る</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7">
-            <v>2030</v>
+            <v>2011</v>
           </cell>
           <cell r="E7" t="str">
-            <v>ダンジョンクリア</v>
+            <v>ダンジョンから出る（確認無し）</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>3010</v>
+            <v>2020</v>
           </cell>
           <cell r="E8" t="str">
-            <v>アーティファクト取得</v>
+            <v>ダンジョン移動</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3020</v>
+            <v>2021</v>
           </cell>
           <cell r="E9" t="str">
-            <v>アイテム取得</v>
+            <v>移動判定なしでダンジョン移動</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>3030</v>
+            <v>2030</v>
           </cell>
           <cell r="E10" t="str">
-            <v>魔法入手</v>
+            <v>ダンジョンクリア</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>4010</v>
+            <v>3010</v>
           </cell>
           <cell r="E11" t="str">
-            <v>仲間を増やす</v>
+            <v>アーティファクト取得</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
-            <v>4011</v>
+            <v>3020</v>
           </cell>
           <cell r="E12" t="str">
-            <v>仲間を外す</v>
+            <v>アイテム取得</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
-            <v>4020</v>
+            <v>3030</v>
           </cell>
           <cell r="E13" t="str">
-            <v>選択して仲間を増やす</v>
+            <v>魔法入手</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14">
-            <v>5010</v>
+            <v>4010</v>
           </cell>
           <cell r="E14" t="str">
-            <v>強制戦闘</v>
+            <v>仲間を増やす</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15">
-            <v>5020</v>
+            <v>4011</v>
           </cell>
           <cell r="E15" t="str">
-            <v>強制ボス戦闘</v>
+            <v>仲間を外す</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16">
-            <v>6010</v>
+            <v>4020</v>
           </cell>
           <cell r="E16" t="str">
-            <v>指定のイベントマスを消す</v>
+            <v>選択して仲間を増やす</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>6011</v>
+            <v>5010</v>
           </cell>
           <cell r="E17" t="str">
-            <v>指定のイベントマスを表示する</v>
+            <v>強制戦闘</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18">
-            <v>6020</v>
+            <v>5020</v>
           </cell>
           <cell r="E18" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+            <v>強制ボス戦闘</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19">
-            <v>6030</v>
+            <v>6010</v>
           </cell>
           <cell r="E19" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
+            <v>指定のイベントマスを消す</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>7010</v>
+            <v>6011</v>
           </cell>
           <cell r="E20" t="str">
-            <v>ダメージ床</v>
+            <v>指定のイベントマスを表示する</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>7020</v>
+            <v>6020</v>
           </cell>
           <cell r="E21" t="str">
-            <v>怨嗟床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22">
-            <v>7021</v>
+            <v>6030</v>
           </cell>
           <cell r="E22" t="str">
-            <v>怨嗟床解除</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23">
-            <v>8010</v>
+            <v>7010</v>
           </cell>
           <cell r="E23" t="str">
-            <v>指定リージョンを開示する</v>
+            <v>ダメージ床</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24">
+            <v>7020</v>
+          </cell>
+          <cell r="E24" t="str">
+            <v>怨嗟床</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="D25">
+            <v>7021</v>
+          </cell>
+          <cell r="E25" t="str">
+            <v>怨嗟床解除</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="D26">
+            <v>8010</v>
+          </cell>
+          <cell r="E26" t="str">
+            <v>指定リージョンを開示する</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="D27">
             <v>9010</v>
           </cell>
-          <cell r="E24" t="str">
+          <cell r="E27" t="str">
             <v>イベント終了明示</v>
           </cell>
         </row>
@@ -1322,10 +1361,10 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F2">
         <v>9</v>
@@ -1449,13 +1488,13 @@
         <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>8</v>
@@ -1464,13 +1503,13 @@
         <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>8</v>
@@ -1481,15 +1520,9 @@
       <c r="O2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
@@ -1528,13 +1561,13 @@
         <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>8</v>
@@ -1543,13 +1576,13 @@
         <v>8</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>8</v>
@@ -1560,15 +1593,9 @@
       <c r="O3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
@@ -1607,13 +1634,11 @@
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>8</v>
@@ -1622,13 +1647,11 @@
         <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>8</v>
@@ -1639,15 +1662,9 @@
       <c r="O4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -1677,22 +1694,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>8</v>
@@ -1701,32 +1718,26 @@
         <v>8</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
@@ -1756,56 +1767,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="M6" s="2"/>
       <c r="N6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -1835,36 +1830,46 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="I7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="P7" s="2"/>
-      <c r="Q7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
@@ -1897,47 +1902,43 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="H8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
@@ -1970,31 +1971,33 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="H9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>8</v>
@@ -2002,15 +2005,9 @@
       <c r="O9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
@@ -2040,19 +2037,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="H10" s="2" t="s">
         <v>9</v>
       </c>
@@ -2062,28 +2061,22 @@
       <c r="J10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
@@ -2113,52 +2106,32 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="O11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
@@ -2188,46 +2161,50 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="G12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
@@ -2260,37 +2237,33 @@
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>8</v>
@@ -2298,15 +2271,9 @@
       <c r="O13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
@@ -2345,13 +2312,10 @@
         <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>8</v>
@@ -2360,13 +2324,13 @@
         <v>8</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>8</v>
@@ -2377,15 +2341,9 @@
       <c r="O14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
@@ -2424,13 +2382,13 @@
         <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>8</v>
@@ -2439,13 +2397,13 @@
         <v>8</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>8</v>
@@ -2456,15 +2414,9 @@
       <c r="O15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
@@ -3660,13 +3612,13 @@
         <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>8</v>
@@ -3675,13 +3627,13 @@
         <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>8</v>
@@ -3692,15 +3644,9 @@
       <c r="O2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
@@ -3739,13 +3685,13 @@
         <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>8</v>
@@ -3754,13 +3700,13 @@
         <v>8</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>8</v>
@@ -3771,15 +3717,9 @@
       <c r="O3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
@@ -3818,13 +3758,11 @@
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>8</v>
@@ -3833,13 +3771,11 @@
         <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>8</v>
@@ -3850,15 +3786,9 @@
       <c r="O4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -3888,22 +3818,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>8</v>
@@ -3912,32 +3842,26 @@
         <v>8</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
@@ -3967,56 +3891,44 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="M6" s="2"/>
       <c r="N6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -4046,36 +3958,46 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="I7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="P7" s="2"/>
-      <c r="Q7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
@@ -4108,47 +4030,43 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="H8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
@@ -4181,31 +4099,33 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="H9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>8</v>
@@ -4213,15 +4133,9 @@
       <c r="O9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
@@ -4251,19 +4165,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="H10" s="2" t="s">
         <v>9</v>
       </c>
@@ -4273,28 +4189,22 @@
       <c r="J10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
@@ -4324,52 +4234,38 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="E11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="M11" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
@@ -4399,46 +4295,50 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="L12" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
@@ -4471,37 +4371,35 @@
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>8</v>
@@ -4509,15 +4407,9 @@
       <c r="O13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
@@ -4556,13 +4448,13 @@
         <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>8</v>
@@ -4571,13 +4463,13 @@
         <v>8</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>8</v>
@@ -4588,15 +4480,9 @@
       <c r="O14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
@@ -4635,13 +4521,13 @@
         <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>8</v>
@@ -4650,13 +4536,13 @@
         <v>8</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>8</v>
@@ -4667,15 +4553,9 @@
       <c r="O15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
@@ -5768,7 +5648,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="7" max="7" width="16.7272727272727" customWidth="1"/>
@@ -5779,34 +5659,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -5814,10 +5694,10 @@
         <v>52</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>3010</v>
@@ -5833,7 +5713,7 @@
         <v>51</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -5847,10 +5727,10 @@
         <v>52</v>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3">
         <v>3010</v>
@@ -5866,10 +5746,10 @@
         <v>53</v>
       </c>
       <c r="I3">
+        <v>12</v>
+      </c>
+      <c r="J3">
         <v>4</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -5880,23 +5760,23 @@
         <v>52</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>3010</v>
       </c>
       <c r="F4">
-        <v>7010</v>
+        <v>3020</v>
       </c>
       <c r="G4" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F4,[1]Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H4">
-        <v>20</v>
+        <v>1200</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5905,7 +5785,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -5913,23 +5793,23 @@
         <v>52</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>3010</v>
       </c>
       <c r="F5">
-        <v>7010</v>
+        <v>9010</v>
       </c>
       <c r="G5" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F5,[1]Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5938,7 +5818,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -5946,29 +5826,29 @@
         <v>52</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="F6">
-        <v>5010</v>
+        <v>1010</v>
       </c>
       <c r="G6" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F6,[1]Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>Adv再生</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>1070</v>
       </c>
       <c r="I6">
-        <v>40020</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -5982,26 +5862,26 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7">
         <v>3010</v>
       </c>
       <c r="F7">
-        <v>5010</v>
+        <v>6010</v>
       </c>
       <c r="G7" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F7,[1]Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>91</v>
       </c>
       <c r="I7">
-        <v>40020</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -6012,23 +5892,23 @@
         <v>52</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>3010</v>
       </c>
       <c r="F8">
-        <v>1010</v>
+        <v>0</v>
       </c>
       <c r="G8" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F8,[1]Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>なし</v>
       </c>
       <c r="H8">
-        <v>1060</v>
+        <v>91</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6045,23 +5925,23 @@
         <v>52</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9">
         <v>3010</v>
       </c>
       <c r="F9">
-        <v>9010</v>
+        <v>5010</v>
       </c>
       <c r="G9" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F9,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -6070,6 +5950,369 @@
         <v>0</v>
       </c>
       <c r="K9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>52</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>3010</v>
+      </c>
+      <c r="F10">
+        <v>8010</v>
+      </c>
+      <c r="G10" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F10,[1]Define!D:D))</f>
+        <v>指定リージョンを開示する</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>52</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>3010</v>
+      </c>
+      <c r="F11">
+        <v>8010</v>
+      </c>
+      <c r="G11" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F11,[1]Define!D:D))</f>
+        <v>指定リージョンを開示する</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>52</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>3010</v>
+      </c>
+      <c r="F12">
+        <v>8010</v>
+      </c>
+      <c r="G12" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F12,[1]Define!D:D))</f>
+        <v>指定リージョンを開示する</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>52</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <v>3010</v>
+      </c>
+      <c r="F13">
+        <v>8010</v>
+      </c>
+      <c r="G13" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F13,[1]Define!D:D))</f>
+        <v>指定リージョンを開示する</v>
+      </c>
+      <c r="H13">
+        <v>4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>52</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
+      <c r="D14">
+        <v>3010</v>
+      </c>
+      <c r="F14">
+        <v>1010</v>
+      </c>
+      <c r="G14" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F14,[1]Define!D:D))</f>
+        <v>Adv再生</v>
+      </c>
+      <c r="H14">
+        <v>110</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>52</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>9</v>
+      </c>
+      <c r="D15">
+        <v>3010</v>
+      </c>
+      <c r="F15">
+        <v>7020</v>
+      </c>
+      <c r="G15" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F15,[1]Define!D:D))</f>
+        <v>怨嗟床</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>52</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>3010</v>
+      </c>
+      <c r="F16">
+        <v>1010</v>
+      </c>
+      <c r="G16" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F16,[1]Define!D:D))</f>
+        <v>Adv再生</v>
+      </c>
+      <c r="H16">
+        <v>120</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17">
+        <v>52</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+      <c r="D17">
+        <v>3010</v>
+      </c>
+      <c r="F17">
+        <v>9010</v>
+      </c>
+      <c r="G17" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F17,[1]Define!D:D))</f>
+        <v>イベント終了明示</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18">
+        <v>52</v>
+      </c>
+      <c r="B18">
+        <v>12</v>
+      </c>
+      <c r="C18">
+        <v>9</v>
+      </c>
+      <c r="D18">
+        <v>3010</v>
+      </c>
+      <c r="F18">
+        <v>1010</v>
+      </c>
+      <c r="G18" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F18,[1]Define!D:D))</f>
+        <v>Adv再生</v>
+      </c>
+      <c r="H18">
+        <v>130</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19">
+        <v>52</v>
+      </c>
+      <c r="B19">
+        <v>12</v>
+      </c>
+      <c r="C19">
+        <v>9</v>
+      </c>
+      <c r="D19">
+        <v>3010</v>
+      </c>
+      <c r="F19">
+        <v>7021</v>
+      </c>
+      <c r="G19" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F19,[1]Define!D:D))</f>
+        <v>怨嗟床解除</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20">
+        <v>52</v>
+      </c>
+      <c r="B20">
+        <v>12</v>
+      </c>
+      <c r="C20">
+        <v>9</v>
+      </c>
+      <c r="D20">
+        <v>3010</v>
+      </c>
+      <c r="F20">
+        <v>9010</v>
+      </c>
+      <c r="G20" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F20,[1]Define!D:D))</f>
+        <v>イベント終了明示</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/Dungeon0052.xlsx
+++ b/Assets/Data/Dungeon0052.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -112,9 +112,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -132,31 +132,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -168,19 +156,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -206,11 +185,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -232,14 +247,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -247,18 +254,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -269,8 +268,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -282,54 +282,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -345,7 +297,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -363,7 +387,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,19 +405,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -405,31 +423,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,7 +441,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,19 +465,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,6 +476,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -490,30 +499,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -534,6 +519,21 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -584,145 +584,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5776,7 +5776,7 @@
         <v>アイテム取得</v>
       </c>
       <c r="H4">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="I4">
         <v>0</v>

--- a/Assets/Data/Dungeon0052.xlsx
+++ b/Assets/Data/Dungeon0052.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -132,6 +132,87 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -141,7 +222,23 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -156,23 +253,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -185,92 +268,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,7 +285,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,7 +297,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -309,7 +339,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -321,13 +357,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -339,133 +453,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,15 +476,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -503,13 +494,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -517,8 +512,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -553,26 +557,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -584,7 +584,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -593,136 +593,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -802,9 +802,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Stages"/>
-      <sheetName val="StageEvents"/>
       <sheetName val="StageEnemyRates"/>
-      <sheetName val="Tutorials"/>
       <sheetName val="TextData"/>
       <sheetName val="Define"/>
     </sheetNames>
@@ -812,9 +810,7 @@
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
+      <sheetData sheetId="3">
         <row r="1">
           <cell r="D1" t="str">
             <v>Type</v>
